--- a/ResourcesPK/pjpConfigurationBulkCreationExcel.xlsx
+++ b/ResourcesPK/pjpConfigurationBulkCreationExcel.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>Distributor*</t>
   </si>
@@ -127,6 +127,15 @@
   </si>
   <si>
     <t>PJP9C63F</t>
+  </si>
+  <si>
+    <t>PJP5206F</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>PJP60A61</t>
   </si>
 </sst>
 </file>
@@ -500,7 +509,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>11</v>
@@ -512,7 +521,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
